--- a/序号3、4内容.xlsx
+++ b/序号3、4内容.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14115" windowHeight="11655"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
